--- a/AAII_Financials/Quarterly/EKTAY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/EKTAY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="92">
   <si>
     <t>EKTAY</t>
   </si>
@@ -656,80 +656,87 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46234</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46142</v>
+      </c>
+      <c r="F7" s="2">
         <v>46053</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45961</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45869</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45777</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45688</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45596</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45504</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45412</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45322</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45230</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45138</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>45046</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44957</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -772,8 +779,14 @@
       <c r="P8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -816,8 +829,14 @@
       <c r="P9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -860,8 +879,14 @@
       <c r="P10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -878,8 +903,10 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -922,8 +949,14 @@
       <c r="P12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -966,8 +999,14 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1010,8 +1049,14 @@
       <c r="P14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1054,8 +1099,14 @@
       <c r="P15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1069,8 +1120,10 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1113,8 +1166,14 @@
       <c r="P17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1157,8 +1216,14 @@
       <c r="P18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1175,8 +1240,10 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1219,8 +1286,14 @@
       <c r="P20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1263,8 +1336,14 @@
       <c r="P21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1307,8 +1386,14 @@
       <c r="P22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1351,8 +1436,14 @@
       <c r="P23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1395,8 +1486,14 @@
       <c r="P24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1439,8 +1536,14 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1483,8 +1586,14 @@
       <c r="P26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1527,8 +1636,14 @@
       <c r="P27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1571,8 +1686,14 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1615,8 +1736,14 @@
       <c r="P29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1659,8 +1786,14 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1703,8 +1836,14 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1747,8 +1886,14 @@
       <c r="P32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1791,8 +1936,14 @@
       <c r="P33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1835,8 +1986,14 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1879,57 +2036,69 @@
       <c r="P35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46234</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46142</v>
+      </c>
+      <c r="F38" s="2">
         <v>46053</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45961</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45869</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45777</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45688</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45596</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45504</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45412</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45322</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45230</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45138</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>45046</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44957</v>
       </c>
     </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1946,8 +2115,10 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1964,52 +2135,60 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>241700</v>
+      </c>
+      <c r="E41" s="3">
+        <v>344500</v>
+      </c>
+      <c r="F41" s="3">
         <v>286600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>271200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>282500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>305300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>324200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>313700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>220500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>253000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>227300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>167200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>225700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>319600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>116500</v>
       </c>
     </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2052,316 +2231,364 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>695400</v>
+      </c>
+      <c r="E43" s="3">
+        <v>670600</v>
+      </c>
+      <c r="F43" s="3">
         <v>842500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>776200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>783300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>699100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>741400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>750200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>760400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>633300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>803300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>817800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>832300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>685900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>831500</v>
       </c>
     </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>366400</v>
+      </c>
+      <c r="E44" s="3">
+        <v>310700</v>
+      </c>
+      <c r="F44" s="3">
         <v>340500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>324900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>310000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>284700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>292100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>318000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>328700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>296700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>342000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>340400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>355900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>299300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>319300</v>
       </c>
     </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>4</v>
+      <c r="E45" s="3">
+        <v>23900</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G45" s="3">
+      <c r="G45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I45" s="3">
         <v>30400</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M45" s="3">
         <v>29000</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q45" s="3">
         <v>25300</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="R45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1303400</v>
+      </c>
+      <c r="E46" s="3">
+        <v>1415300</v>
+      </c>
+      <c r="F46" s="3">
         <v>1469400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>1372400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>1375800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>1386100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>1357700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>1381900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>1309700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>1270800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>1372400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>1325300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>1413900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>1401500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>1267300</v>
       </c>
     </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E47" s="3" t="s">
-        <v>4</v>
+      <c r="E47" s="3">
+        <v>3000</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G47" s="3">
+      <c r="G47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I47" s="3">
         <v>3000</v>
       </c>
-      <c r="H47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K47" s="3">
+      <c r="K47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M47" s="3">
         <v>3100</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O47" s="3">
+      <c r="O47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q47" s="3">
         <v>2600</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="R47" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>170200</v>
+      </c>
+      <c r="E48" s="3">
+        <v>177000</v>
+      </c>
+      <c r="F48" s="3">
         <v>183300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>183400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>190500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>197000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>191400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>199500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>200200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>202700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>208100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>168400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>169100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>170900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>171600</v>
       </c>
     </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1155100</v>
+      </c>
+      <c r="E49" s="3">
+        <v>787300</v>
+      </c>
+      <c r="F49" s="3">
         <v>1282500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>1243100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>1239500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>800000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>1258200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>1282600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>1244700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>766900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>1218800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>1170800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>1187300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>769100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>1099400</v>
       </c>
     </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2404,8 +2631,14 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2448,52 +2681,64 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>73700</v>
+      </c>
+      <c r="E52" s="3">
+        <v>4300</v>
+      </c>
+      <c r="F52" s="3">
         <v>82600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>80900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>84500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>8500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>88700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>95400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>95300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>5000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>102100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>92800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>99300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>8200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>69500</v>
       </c>
     </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2536,52 +2781,64 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2797300</v>
+      </c>
+      <c r="E54" s="3">
+        <v>2911600</v>
+      </c>
+      <c r="F54" s="3">
         <v>3121400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>2973100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>2983400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>2993600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>2981400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>3044800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>2930600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>2860000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>2970200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>2827600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>2939300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>2886700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>2676000</v>
       </c>
     </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2598,8 +2855,10 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2616,272 +2875,310 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>182400</v>
+      </c>
+      <c r="E57" s="3">
+        <v>202900</v>
+      </c>
+      <c r="F57" s="3">
         <v>167900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>167800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>168200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>189800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>140800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>155100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>146500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>141100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>144500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>153900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>161200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>176400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>133000</v>
       </c>
     </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>283900</v>
+      </c>
+      <c r="E58" s="3">
+        <v>344900</v>
+      </c>
+      <c r="F58" s="3">
         <v>229800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>115400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>113100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>42500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>140500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>182900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>175300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>122500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>33000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>21200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>22100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>24400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>72500</v>
       </c>
     </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>836200</v>
+      </c>
+      <c r="E59" s="3">
+        <v>892100</v>
+      </c>
+      <c r="F59" s="3">
         <v>910900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>814300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>812200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>855600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>797100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>778200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>821900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>834900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>886300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>873500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>901800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>865900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>822200</v>
       </c>
     </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1508400</v>
+      </c>
+      <c r="E60" s="3">
+        <v>1627100</v>
+      </c>
+      <c r="F60" s="3">
         <v>1551000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>1322900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>1305000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>1275700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>1277500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>1311600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>1321200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>1274300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>1253800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>1234200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>1267100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>1238800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>1213000</v>
       </c>
     </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>432200</v>
+      </c>
+      <c r="E61" s="3">
+        <v>447000</v>
+      </c>
+      <c r="F61" s="3">
         <v>591600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>685100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>679000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>739300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>661300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>686500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>546900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>537300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>657300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>591200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>621200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>625700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>467000</v>
       </c>
     </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>59600</v>
+      </c>
+      <c r="E62" s="3">
+        <v>23300</v>
+      </c>
+      <c r="F62" s="3">
         <v>75200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>71000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>64900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>21800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>62800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>66900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>63600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>15600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>28000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>36600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>33000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>13700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>28200</v>
       </c>
     </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2924,8 +3221,14 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2968,8 +3271,14 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3012,52 +3321,64 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2000100</v>
+      </c>
+      <c r="E66" s="3">
+        <v>2139500</v>
+      </c>
+      <c r="F66" s="3">
         <v>2217800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>2079000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>2048800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>2079500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>2001600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>2065100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>1931700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>1878600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>1979300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>1900200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>1964800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>1937700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>1754800</v>
       </c>
     </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3074,8 +3395,10 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3118,8 +3441,14 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3162,8 +3491,14 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3206,8 +3541,14 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3250,52 +3591,64 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E72" s="3" t="s">
-        <v>4</v>
+      <c r="E72" s="3">
+        <v>563300</v>
       </c>
       <c r="F72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G72" s="3">
+      <c r="G72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I72" s="3">
         <v>686500</v>
       </c>
-      <c r="H72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K72" s="3">
+      <c r="K72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M72" s="3">
         <v>665500</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O72" s="3">
+      <c r="O72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q72" s="3">
         <v>673900</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="R72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3338,8 +3691,14 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3382,8 +3741,14 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3426,52 +3791,64 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>793000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>766800</v>
+      </c>
+      <c r="F76" s="3">
         <v>898700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>889600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>929900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>909400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>975700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>975100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>998400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>980900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>990400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>927000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>974100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>948500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>920800</v>
       </c>
     </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3514,57 +3891,69 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46234</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46142</v>
+      </c>
+      <c r="F80" s="2">
         <v>46053</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45961</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45869</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45777</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45688</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45596</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45504</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45412</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45322</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45230</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45138</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>45046</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44957</v>
       </c>
     </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3607,8 +3996,14 @@
       <c r="P81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3625,52 +4020,60 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>11000</v>
+      </c>
+      <c r="E83" s="3">
+        <v>-36500</v>
+      </c>
+      <c r="F83" s="3">
         <v>10300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>10900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>11100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>11400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>10300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>10500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>13100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>10700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>10500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>11200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>-23300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>11300</v>
       </c>
     </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3713,8 +4116,14 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3757,8 +4166,14 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3801,8 +4216,14 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3845,8 +4266,14 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3889,52 +4316,64 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>0</v>
+      </c>
+      <c r="E89" s="3">
+        <v>149100</v>
+      </c>
+      <c r="F89" s="3">
         <v>60100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>67100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-8800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>162000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>99100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>42700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-46000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>119900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>103600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>55700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-52500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>194100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>21500</v>
       </c>
     </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3951,52 +4390,60 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="F91" s="3">
         <v>-3700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-2300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-3000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-3000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-4100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-6200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-5700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-5900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-9400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-4000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-4100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-5000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-7100</v>
       </c>
     </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4039,8 +4486,14 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4083,52 +4536,64 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-35800</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-25700</v>
+      </c>
+      <c r="F94" s="3">
         <v>-31500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-29500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-28000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-33100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-33600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-53700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-38200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-40400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-49700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-55200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-33000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-42000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-40700</v>
       </c>
     </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4145,52 +4610,60 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>4</v>
+      <c r="D96" s="3">
+        <v>700</v>
       </c>
       <c r="E96" s="3">
+        <v>49600</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G96" s="3">
         <v>48200</v>
       </c>
-      <c r="F96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I96" s="3">
         <v>47400</v>
       </c>
-      <c r="H96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K96" s="3">
         <v>42900</v>
       </c>
-      <c r="J96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M96" s="3">
         <v>41700</v>
       </c>
-      <c r="L96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O96" s="3">
         <v>41100</v>
       </c>
-      <c r="N96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q96" s="3">
         <v>44700</v>
       </c>
-      <c r="P96" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="R96" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4233,8 +4706,14 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4277,8 +4756,14 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4321,136 +4806,160 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-60800</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-56800</v>
+      </c>
+      <c r="F100" s="3">
         <v>-28000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-55000</v>
       </c>
-      <c r="F100" s="3">
-        <v>12900</v>
-      </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
+        <v>12800</v>
+      </c>
+      <c r="I100" s="3">
         <v>-169900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-46200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>97900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>47000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-47600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>2900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-48400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-6200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>51900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-9400</v>
       </c>
     </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-23800</v>
+      </c>
+      <c r="F101" s="3">
         <v>1500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>5600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-1600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>7200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-10100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>3100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>5000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-3100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-1900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>4500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>-1600</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>3000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>15900</v>
       </c>
     </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-92700</v>
+      </c>
+      <c r="E102" s="3">
+        <v>70100</v>
+      </c>
+      <c r="F102" s="3">
         <v>-4100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-19500</v>
       </c>
-      <c r="F102" s="3">
-        <v>-20000</v>
-      </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
+        <v>-20100</v>
+      </c>
+      <c r="I102" s="3">
         <v>-64800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>20800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>92500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-38700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>39100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>46800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-44700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-86800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>200800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-30400</v>
       </c>
     </row>
